--- a/Featured fixtures.xlsx
+++ b/Featured fixtures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16762" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16759" uniqueCount="503">
   <si>
     <t>Date</t>
   </si>
@@ -1492,22 +1492,37 @@
     <t>Wanda Metropolitano</t>
   </si>
   <si>
-    <t>Derby County</t>
+    <t>Man City</t>
+  </si>
+  <si>
+    <t>PSG</t>
   </si>
   <si>
     <t>Birmingham City</t>
   </si>
   <si>
-    <t>Wolverhampton Wanderers</t>
-  </si>
-  <si>
     <t>Leeds United</t>
   </si>
   <si>
-    <t>Ipswich Town</t>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Paris</t>
+  </si>
+  <si>
+    <t>Parc de Princes</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
   </si>
   <si>
     <t>Brighton and Hove Albion</t>
+  </si>
+  <si>
+    <t>Celtic</t>
+  </si>
+  <si>
+    <t>Derby County</t>
   </si>
 </sst>
 </file>
@@ -1561,7 +1576,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1606,6 +1621,10 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -58281,23 +58300,23 @@
       <c r="A9" s="4">
         <v>46309.0</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>266</v>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>309</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>492</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>291</v>
+        <v>493</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="10">
@@ -58309,7 +58328,7 @@
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>235</v>
@@ -58321,24 +58340,18 @@
       <c r="A11" s="4">
         <v>46311.0</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>150</v>
+      <c r="B11" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="11" t="s">
+        <v>492</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>152</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12">
       <c r="A12" s="4">
@@ -58420,16 +58433,16 @@
         <v>276</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>494</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>15</v>
+        <v>493</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>497</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="16">
@@ -58440,51 +58453,50 @@
         <v>482</v>
       </c>
       <c r="C16" s="13"/>
-      <c r="D16" s="11" t="s">
-        <v>485</v>
+      <c r="D16" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>182</v>
+        <v>499</v>
       </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
     </row>
     <row r="17">
-      <c r="A17" s="4">
+      <c r="A17" s="12">
         <v>46317.0</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>482</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="C17" s="15"/>
+      <c r="D17" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="16" t="s">
         <v>484</v>
       </c>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18">
-      <c r="A18" s="4">
+      <c r="A18" s="12">
         <v>46318.0</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>308</v>
-      </c>
+      <c r="D18" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="19">
       <c r="A19" s="4">
@@ -58523,7 +58535,7 @@
         <v>173</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>173</v>
@@ -58541,10 +58553,10 @@
       </c>
       <c r="C21" s="13"/>
       <c r="D21" s="10" t="s">
-        <v>65</v>
+        <v>501</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
@@ -58567,26 +58579,38 @@
       <c r="G22" s="14"/>
     </row>
     <row r="23">
-      <c r="A23" s="4">
+      <c r="A23" s="12">
         <v>46323.0</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="B23" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="16" t="s">
         <v>486</v>
       </c>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24">
-      <c r="A24" s="4">
+      <c r="A24" s="12">
         <v>46324.0</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>492</v>
-      </c>
-      <c r="E24" s="9" t="s">
+      <c r="B24" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="16" t="s">
+        <v>502</v>
+      </c>
+      <c r="E24" s="16" t="s">
         <v>495</v>
       </c>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="4">

--- a/Featured fixtures.xlsx
+++ b/Featured fixtures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16759" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16837" uniqueCount="511">
   <si>
     <t>Date</t>
   </si>
@@ -1524,6 +1524,30 @@
   <si>
     <t>Derby County</t>
   </si>
+  <si>
+    <t>AC Milan</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Roma</t>
+  </si>
+  <si>
+    <t>Napoli</t>
+  </si>
+  <si>
+    <t>Machester United</t>
+  </si>
+  <si>
+    <t>Blackburn Rovers</t>
+  </si>
+  <si>
+    <t>Bolton Wanderers</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
 </sst>
 </file>
 
@@ -58754,6 +58778,12 @@
       <c r="A31" s="4">
         <v>46331.0</v>
       </c>
+      <c r="D31" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4">
@@ -58828,140 +58858,368 @@
       <c r="A35" s="4">
         <v>46335.0</v>
       </c>
+      <c r="D35" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4">
         <v>46336.0</v>
       </c>
+      <c r="D36" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>504</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4">
         <v>46337.0</v>
       </c>
+      <c r="D37" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4">
         <v>46338.0</v>
       </c>
+      <c r="D38" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4">
         <v>46339.0</v>
       </c>
+      <c r="D39" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4">
         <v>46340.0</v>
       </c>
+      <c r="D40" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4">
         <v>46341.0</v>
       </c>
+      <c r="D41" s="9" t="s">
+        <v>506</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>507</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4">
         <v>46342.0</v>
       </c>
+      <c r="D42" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4">
         <v>46343.0</v>
       </c>
+      <c r="D43" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4">
         <v>46344.0</v>
       </c>
+      <c r="D44" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4">
         <v>46345.0</v>
       </c>
+      <c r="D45" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4">
         <v>46346.0</v>
       </c>
+      <c r="D46" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4">
         <v>46347.0</v>
       </c>
+      <c r="D47" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4">
         <v>46348.0</v>
       </c>
+      <c r="D48" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4">
         <v>46349.0</v>
       </c>
+      <c r="D49" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>510</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4">
         <v>46350.0</v>
       </c>
+      <c r="D50" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4">
         <v>46351.0</v>
       </c>
+      <c r="D51" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>500</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4">
         <v>46352.0</v>
       </c>
+      <c r="D52" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4">
         <v>46353.0</v>
       </c>
+      <c r="D53" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4">
         <v>46354.0</v>
       </c>
+      <c r="D54" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4">
         <v>46355.0</v>
       </c>
+      <c r="D55" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4">
         <v>46356.0</v>
       </c>
+      <c r="D56" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4">
         <v>46357.0</v>
       </c>
+      <c r="D57" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4">
         <v>46358.0</v>
       </c>
+      <c r="D58" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4">
         <v>46359.0</v>
       </c>
+      <c r="D59" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4">
         <v>46360.0</v>
       </c>
+      <c r="D60" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4">
         <v>46361.0</v>
       </c>
+      <c r="D61" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4">
         <v>46362.0</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="63">

--- a/Featured fixtures.xlsx
+++ b/Featured fixtures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16837" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16837" uniqueCount="510">
   <si>
     <t>Date</t>
   </si>
@@ -1522,9 +1522,6 @@
     <t>Celtic</t>
   </si>
   <si>
-    <t>Derby County</t>
-  </si>
-  <si>
     <t>AC Milan</t>
   </si>
   <si>
@@ -58628,10 +58625,10 @@
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="16" t="s">
-        <v>502</v>
+        <v>171</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>495</v>
+        <v>488</v>
       </c>
       <c r="F24" s="15"/>
       <c r="G24" s="15"/>
@@ -58779,7 +58776,7 @@
         <v>46331.0</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>235</v>
@@ -58873,7 +58870,7 @@
         <v>486</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="37">
@@ -58892,7 +58889,7 @@
         <v>46338.0</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>173</v>
@@ -58925,10 +58922,10 @@
         <v>46341.0</v>
       </c>
       <c r="D41" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="E41" s="9" t="s">
         <v>506</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="42">
@@ -58947,7 +58944,7 @@
         <v>46343.0</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>486</v>
@@ -58958,7 +58955,7 @@
         <v>46344.0</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>499</v>
@@ -58969,7 +58966,7 @@
         <v>46345.0</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>496</v>
@@ -59016,7 +59013,7 @@
         <v>162</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="50">
@@ -59027,7 +59024,7 @@
         <v>493</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="51">
@@ -59035,7 +59032,7 @@
         <v>46351.0</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>500</v>

--- a/Featured fixtures.xlsx
+++ b/Featured fixtures.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16837" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16833" uniqueCount="510">
   <si>
     <t>Date</t>
   </si>
@@ -1522,13 +1522,13 @@
     <t>Celtic</t>
   </si>
   <si>
+    <t>Roma</t>
+  </si>
+  <si>
     <t>AC Milan</t>
   </si>
   <si>
     <t>Sporting CP</t>
-  </si>
-  <si>
-    <t>Roma</t>
   </si>
   <si>
     <t>Napoli</t>
@@ -58641,19 +58641,19 @@
         <v>10</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>50</v>
+        <v>246</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>53</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26">
@@ -58667,16 +58667,16 @@
         <v>297</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="F26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>259</v>
+      <c r="G26" s="2" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="27">
@@ -58735,18 +58735,14 @@
       <c r="C29" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="D29" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" s="4">
@@ -58758,28 +58754,24 @@
       <c r="C30" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>157</v>
-      </c>
+      <c r="D30" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>502</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" s="4">
         <v>46331.0</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32">
@@ -58870,7 +58862,7 @@
         <v>486</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="37">
@@ -58889,7 +58881,7 @@
         <v>46338.0</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>173</v>
@@ -59024,7 +59016,7 @@
         <v>493</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="51">
@@ -59032,7 +59024,7 @@
         <v>46351.0</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>500</v>
